--- a/data/lluvia.xlsx
+++ b/data/lluvia.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FJRA\FORMACION\ROBOTIC\esp32\proj02_esp32_TemperatureMeasures\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFB49E9-DDA8-4B2D-95B6-DB85603A63FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0486BE1A-9500-4924-88C6-4C0DDCF15CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1872" yWindow="1872" windowWidth="15660" windowHeight="9252" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,13 +57,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -74,14 +88,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{689032C3-05D6-4C66-9496-F79BEFD62344}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -359,106 +377,627 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B69"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>20260221</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <f>A3-1</f>
+        <v>20260222</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f>A2+1</f>
-        <v>20260222</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <f>A4-1</f>
+        <v>20260223</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f t="shared" ref="A4:A11" si="0">A3+1</f>
-        <v>20260223</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <f>A5-1</f>
+        <v>20260224</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f t="shared" si="0"/>
-        <v>20260224</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <f>A6-1</f>
+        <v>20260225</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f t="shared" si="0"/>
-        <v>20260225</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <f>A7-1</f>
+        <v>20260226</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f t="shared" si="0"/>
-        <v>20260226</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <f>A8-1</f>
+        <v>20260227</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f t="shared" si="0"/>
-        <v>20260227</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>20260228</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" si="0"/>
-        <v>20260228</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
+        <f>A10-1</f>
         <v>20260301</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <f t="shared" si="0"/>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>20260302</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f t="shared" ref="A11:A67" si="0">A10+1</f>
+        <v>20260303</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>20260304</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>20260305</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>20260306</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>20260307</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>20260308</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>20260309</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>20260310</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>20260311</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>20260312</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>20260313</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>20260314</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>20260315</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>20260316</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>20260317</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>20260318</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>20260319</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>20260320</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>20260321</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>20260322</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>20260323</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>20260324</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>20260325</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>20260326</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>20260327</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>20260328</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>20260329</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>20260330</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>20260331</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>20260401</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>20260402</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>20260403</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>20260404</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>20260405</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>20260406</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>20260407</v>
+      </c>
+      <c r="B46" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>20260408</v>
+      </c>
+      <c r="B47" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>20260409</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>20260410</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>20260411</v>
+      </c>
+      <c r="B50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>20260412</v>
+      </c>
+      <c r="B51" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>20260413</v>
+      </c>
+      <c r="B52" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>20260414</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>20260415</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>20260416</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>20260417</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>20260418</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>20260419</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>20260420</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>20260421</v>
+      </c>
+      <c r="B60" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>20260422</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>20260423</v>
+      </c>
+      <c r="B62" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>20260424</v>
+      </c>
+      <c r="B63" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>20260425</v>
+      </c>
+      <c r="B64" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>20260426</v>
+      </c>
+      <c r="B65" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>20260427</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>20260428</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B68" s="2"/>
+    </row>
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B69" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{473FE26D-A869-4FF3-B9AC-DFC14E7BA5DD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>